--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714766</v>
+        <v>113712541</v>
       </c>
       <c r="B2" t="n">
-        <v>90142</v>
+        <v>91028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>4745</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654351</v>
+        <v>654248</v>
       </c>
       <c r="R2" t="n">
-        <v>7036502</v>
+        <v>7036074</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712563</v>
+        <v>113712556</v>
       </c>
       <c r="B3" t="n">
-        <v>78794</v>
+        <v>90686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654366</v>
+        <v>654461</v>
       </c>
       <c r="R3" t="n">
-        <v>7036185</v>
+        <v>7036447</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714768</v>
+        <v>113714767</v>
       </c>
       <c r="B5" t="n">
-        <v>90142</v>
+        <v>56955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654442</v>
+        <v>654323</v>
       </c>
       <c r="R5" t="n">
-        <v>7036406</v>
+        <v>7036510</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,7 +1078,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714755</v>
+        <v>113714762</v>
       </c>
       <c r="B6" t="n">
-        <v>91028</v>
+        <v>90518</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1125,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tallriska</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654248</v>
+        <v>654249</v>
       </c>
       <c r="R6" t="n">
-        <v>7036074</v>
+        <v>7036581</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714773</v>
+        <v>113714768</v>
       </c>
       <c r="B7" t="n">
-        <v>90131</v>
+        <v>90142</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654536</v>
+        <v>654442</v>
       </c>
       <c r="R7" t="n">
-        <v>7036336</v>
+        <v>7036406</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714769</v>
+        <v>113712542</v>
       </c>
       <c r="B8" t="n">
-        <v>90142</v>
+        <v>78794</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654469</v>
+        <v>654257</v>
       </c>
       <c r="R8" t="n">
-        <v>7036416</v>
+        <v>7036088</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714767</v>
+        <v>113712563</v>
       </c>
       <c r="B9" t="n">
-        <v>56955</v>
+        <v>78794</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654323</v>
+        <v>654366</v>
       </c>
       <c r="R9" t="n">
-        <v>7036510</v>
+        <v>7036185</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1498,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712540</v>
+        <v>113712562</v>
       </c>
       <c r="B10" t="n">
-        <v>78794</v>
+        <v>90142</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654269</v>
+        <v>654383</v>
       </c>
       <c r="R10" t="n">
-        <v>7035993</v>
+        <v>7036207</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712551</v>
+        <v>113712559</v>
       </c>
       <c r="B12" t="n">
-        <v>78201</v>
+        <v>90131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654290</v>
+        <v>654536</v>
       </c>
       <c r="R12" t="n">
-        <v>7036546</v>
+        <v>7036336</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714770</v>
+        <v>113712540</v>
       </c>
       <c r="B13" t="n">
-        <v>90686</v>
+        <v>78794</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2046</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vit aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654461</v>
+        <v>654269</v>
       </c>
       <c r="R13" t="n">
-        <v>7036447</v>
+        <v>7035993</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,11 +1927,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712562</v>
+        <v>113714765</v>
       </c>
       <c r="B14" t="n">
-        <v>90142</v>
+        <v>78201</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654383</v>
+        <v>654290</v>
       </c>
       <c r="R14" t="n">
-        <v>7036207</v>
+        <v>7036546</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2043,6 +2033,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712542</v>
+        <v>113712552</v>
       </c>
       <c r="B15" t="n">
-        <v>78794</v>
+        <v>90142</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654257</v>
+        <v>654351</v>
       </c>
       <c r="R15" t="n">
-        <v>7036088</v>
+        <v>7036502</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2179,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714762</v>
+        <v>113712555</v>
       </c>
       <c r="B16" t="n">
-        <v>90518</v>
+        <v>90142</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,20 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>1205</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654249</v>
+        <v>654469</v>
       </c>
       <c r="R16" t="n">
-        <v>7036581</v>
+        <v>7036416</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712541</v>
+        <v>113714766</v>
       </c>
       <c r="B2" t="n">
-        <v>91028</v>
+        <v>90146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654248</v>
+        <v>654351</v>
       </c>
       <c r="R2" t="n">
-        <v>7036074</v>
+        <v>7036502</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712556</v>
+        <v>113714754</v>
       </c>
       <c r="B3" t="n">
-        <v>90686</v>
+        <v>78794</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2046</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vit aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654461</v>
+        <v>654269</v>
       </c>
       <c r="R3" t="n">
-        <v>7036447</v>
+        <v>7035993</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714767</v>
+        <v>113714773</v>
       </c>
       <c r="B5" t="n">
-        <v>56955</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654323</v>
+        <v>654536</v>
       </c>
       <c r="R5" t="n">
-        <v>7036510</v>
+        <v>7036336</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714762</v>
+        <v>113712555</v>
       </c>
       <c r="B6" t="n">
-        <v>90518</v>
+        <v>90146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,20 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1205</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654249</v>
+        <v>654469</v>
       </c>
       <c r="R6" t="n">
-        <v>7036581</v>
+        <v>7036416</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714768</v>
+        <v>113712551</v>
       </c>
       <c r="B7" t="n">
-        <v>90142</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654442</v>
+        <v>654290</v>
       </c>
       <c r="R7" t="n">
-        <v>7036406</v>
+        <v>7036546</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712542</v>
+        <v>113712563</v>
       </c>
       <c r="B8" t="n">
         <v>78794</v>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654257</v>
+        <v>654366</v>
       </c>
       <c r="R8" t="n">
-        <v>7036088</v>
+        <v>7036185</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712563</v>
+        <v>113712541</v>
       </c>
       <c r="B9" t="n">
-        <v>78794</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4745</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654366</v>
+        <v>654248</v>
       </c>
       <c r="R9" t="n">
-        <v>7036185</v>
+        <v>7036074</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712562</v>
+        <v>113712556</v>
       </c>
       <c r="B10" t="n">
-        <v>90142</v>
+        <v>90690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>2046</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654383</v>
+        <v>654461</v>
       </c>
       <c r="R10" t="n">
-        <v>7036207</v>
+        <v>7036447</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1609,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712560</v>
+        <v>113712548</v>
       </c>
       <c r="B11" t="n">
-        <v>78794</v>
+        <v>90522</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1655,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654479</v>
+        <v>654249</v>
       </c>
       <c r="R11" t="n">
-        <v>7036198</v>
+        <v>7036581</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712559</v>
+        <v>113714767</v>
       </c>
       <c r="B12" t="n">
-        <v>90131</v>
+        <v>56955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654536</v>
+        <v>654323</v>
       </c>
       <c r="R12" t="n">
-        <v>7036336</v>
+        <v>7036510</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712540</v>
+        <v>113714774</v>
       </c>
       <c r="B13" t="n">
         <v>78794</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654269</v>
+        <v>654479</v>
       </c>
       <c r="R13" t="n">
-        <v>7035993</v>
+        <v>7036198</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714765</v>
+        <v>113712542</v>
       </c>
       <c r="B14" t="n">
-        <v>78201</v>
+        <v>78794</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654290</v>
+        <v>654257</v>
       </c>
       <c r="R14" t="n">
-        <v>7036546</v>
+        <v>7036088</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2033,11 +2033,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712552</v>
+        <v>113714775</v>
       </c>
       <c r="B15" t="n">
-        <v>90142</v>
+        <v>90146</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654351</v>
+        <v>654383</v>
       </c>
       <c r="R15" t="n">
-        <v>7036502</v>
+        <v>7036207</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2174,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712555</v>
+        <v>113712554</v>
       </c>
       <c r="B16" t="n">
-        <v>90142</v>
+        <v>90146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654469</v>
+        <v>654442</v>
       </c>
       <c r="R16" t="n">
-        <v>7036416</v>
+        <v>7036406</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2250,6 +2245,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714766</v>
+        <v>113714770</v>
       </c>
       <c r="B2" t="n">
-        <v>90146</v>
+        <v>90690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>2046</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654351</v>
+        <v>654461</v>
       </c>
       <c r="R2" t="n">
-        <v>7036502</v>
+        <v>7036447</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714754</v>
+        <v>113712554</v>
       </c>
       <c r="B3" t="n">
-        <v>78794</v>
+        <v>90146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654269</v>
+        <v>654442</v>
       </c>
       <c r="R3" t="n">
-        <v>7035993</v>
+        <v>7036406</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714777</v>
+        <v>113714756</v>
       </c>
       <c r="B4" t="n">
-        <v>77953</v>
+        <v>78794</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654309</v>
+        <v>654257</v>
       </c>
       <c r="R4" t="n">
-        <v>7036185</v>
+        <v>7036088</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714773</v>
+        <v>113712541</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654536</v>
+        <v>654248</v>
       </c>
       <c r="R5" t="n">
-        <v>7036336</v>
+        <v>7036074</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712555</v>
+        <v>113714769</v>
       </c>
       <c r="B6" t="n">
         <v>90146</v>
@@ -1205,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712551</v>
+        <v>113714766</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>90146</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654290</v>
+        <v>654351</v>
       </c>
       <c r="R7" t="n">
-        <v>7036546</v>
+        <v>7036502</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712563</v>
+        <v>113712559</v>
       </c>
       <c r="B8" t="n">
-        <v>78794</v>
+        <v>90135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654366</v>
+        <v>654536</v>
       </c>
       <c r="R8" t="n">
-        <v>7036185</v>
+        <v>7036336</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712541</v>
+        <v>113714754</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>78794</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4745</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654248</v>
+        <v>654269</v>
       </c>
       <c r="R9" t="n">
-        <v>7036074</v>
+        <v>7035993</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712556</v>
+        <v>113712564</v>
       </c>
       <c r="B10" t="n">
-        <v>90690</v>
+        <v>77953</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2046</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vit aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654461</v>
+        <v>654309</v>
       </c>
       <c r="R10" t="n">
-        <v>7036447</v>
+        <v>7036185</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712548</v>
+        <v>113714776</v>
       </c>
       <c r="B11" t="n">
-        <v>90522</v>
+        <v>78794</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,16 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654249</v>
+        <v>654366</v>
       </c>
       <c r="R11" t="n">
-        <v>7036581</v>
+        <v>7036185</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714767</v>
+        <v>113712548</v>
       </c>
       <c r="B12" t="n">
-        <v>56955</v>
+        <v>90522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654323</v>
+        <v>654249</v>
       </c>
       <c r="R12" t="n">
-        <v>7036510</v>
+        <v>7036581</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714774</v>
+        <v>113712562</v>
       </c>
       <c r="B13" t="n">
-        <v>78794</v>
+        <v>90146</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654479</v>
+        <v>654383</v>
       </c>
       <c r="R13" t="n">
-        <v>7036198</v>
+        <v>7036207</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,7 +1952,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712542</v>
+        <v>113714774</v>
       </c>
       <c r="B14" t="n">
         <v>78794</v>
@@ -1997,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654257</v>
+        <v>654479</v>
       </c>
       <c r="R14" t="n">
-        <v>7036088</v>
+        <v>7036198</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714775</v>
+        <v>113714767</v>
       </c>
       <c r="B15" t="n">
-        <v>90146</v>
+        <v>56955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654383</v>
+        <v>654323</v>
       </c>
       <c r="R15" t="n">
-        <v>7036207</v>
+        <v>7036510</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2139,6 +2134,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712554</v>
+        <v>113714765</v>
       </c>
       <c r="B16" t="n">
-        <v>90146</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654442</v>
+        <v>654290</v>
       </c>
       <c r="R16" t="n">
-        <v>7036406</v>
+        <v>7036546</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714770</v>
+        <v>113712553</v>
       </c>
       <c r="B2" t="n">
-        <v>90690</v>
+        <v>56955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2046</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vit aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654461</v>
+        <v>654323</v>
       </c>
       <c r="R2" t="n">
-        <v>7036447</v>
+        <v>7036510</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gammal fruktkropp</t>
+          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712554</v>
+        <v>113712559</v>
       </c>
       <c r="B3" t="n">
-        <v>90146</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654442</v>
+        <v>654536</v>
       </c>
       <c r="R3" t="n">
-        <v>7036406</v>
+        <v>7036336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714756</v>
+        <v>113714769</v>
       </c>
       <c r="B4" t="n">
-        <v>78794</v>
+        <v>90146</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654257</v>
+        <v>654469</v>
       </c>
       <c r="R4" t="n">
-        <v>7036088</v>
+        <v>7036416</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712541</v>
+        <v>113714762</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>90522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1014,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4745</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallriska</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654248</v>
+        <v>654249</v>
       </c>
       <c r="R5" t="n">
-        <v>7036074</v>
+        <v>7036581</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714769</v>
+        <v>113712540</v>
       </c>
       <c r="B6" t="n">
-        <v>90146</v>
+        <v>78794</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654469</v>
+        <v>654269</v>
       </c>
       <c r="R6" t="n">
-        <v>7036416</v>
+        <v>7035993</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714766</v>
+        <v>113714756</v>
       </c>
       <c r="B7" t="n">
-        <v>90146</v>
+        <v>78794</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654351</v>
+        <v>654257</v>
       </c>
       <c r="R7" t="n">
-        <v>7036502</v>
+        <v>7036088</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712559</v>
+        <v>113714755</v>
       </c>
       <c r="B8" t="n">
-        <v>90135</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4745</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654536</v>
+        <v>654248</v>
       </c>
       <c r="R8" t="n">
-        <v>7036336</v>
+        <v>7036074</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714754</v>
+        <v>113714765</v>
       </c>
       <c r="B9" t="n">
-        <v>78794</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654269</v>
+        <v>654290</v>
       </c>
       <c r="R9" t="n">
-        <v>7035993</v>
+        <v>7036546</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712564</v>
+        <v>113712563</v>
       </c>
       <c r="B10" t="n">
-        <v>77953</v>
+        <v>78794</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,7 +1568,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654309</v>
+        <v>654366</v>
       </c>
       <c r="R10" t="n">
         <v>7036185</v>
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714776</v>
+        <v>113714777</v>
       </c>
       <c r="B11" t="n">
-        <v>78794</v>
+        <v>77953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,7 +1674,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654366</v>
+        <v>654309</v>
       </c>
       <c r="R11" t="n">
         <v>7036185</v>
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712548</v>
+        <v>113712560</v>
       </c>
       <c r="B12" t="n">
-        <v>90522</v>
+        <v>78794</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,16 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654249</v>
+        <v>654479</v>
       </c>
       <c r="R12" t="n">
-        <v>7036581</v>
+        <v>7036198</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714774</v>
+        <v>113714768</v>
       </c>
       <c r="B14" t="n">
-        <v>78794</v>
+        <v>90146</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654479</v>
+        <v>654442</v>
       </c>
       <c r="R14" t="n">
-        <v>7036198</v>
+        <v>7036406</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2028,6 +2028,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714767</v>
+        <v>113714766</v>
       </c>
       <c r="B15" t="n">
-        <v>56955</v>
+        <v>90146</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654323</v>
+        <v>654351</v>
       </c>
       <c r="R15" t="n">
-        <v>7036510</v>
+        <v>7036502</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2134,11 +2139,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714765</v>
+        <v>113712556</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>90690</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2046</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654290</v>
+        <v>654461</v>
       </c>
       <c r="R16" t="n">
-        <v>7036546</v>
+        <v>7036447</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tallstammar</t>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712553</v>
+        <v>113712564</v>
       </c>
       <c r="B2" t="n">
-        <v>56955</v>
+        <v>77953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654323</v>
+        <v>654309</v>
       </c>
       <c r="R2" t="n">
-        <v>7036510</v>
+        <v>7036185</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712559</v>
+        <v>113712542</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>78794</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654536</v>
+        <v>654257</v>
       </c>
       <c r="R3" t="n">
-        <v>7036336</v>
+        <v>7036088</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714769</v>
+        <v>113714774</v>
       </c>
       <c r="B4" t="n">
-        <v>90146</v>
+        <v>78794</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654469</v>
+        <v>654479</v>
       </c>
       <c r="R4" t="n">
-        <v>7036416</v>
+        <v>7036198</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714762</v>
+        <v>113714754</v>
       </c>
       <c r="B5" t="n">
-        <v>90522</v>
+        <v>78794</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,16 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654249</v>
+        <v>654269</v>
       </c>
       <c r="R5" t="n">
-        <v>7036581</v>
+        <v>7035993</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712540</v>
+        <v>113714768</v>
       </c>
       <c r="B6" t="n">
-        <v>78794</v>
+        <v>90146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654269</v>
+        <v>654442</v>
       </c>
       <c r="R6" t="n">
-        <v>7035993</v>
+        <v>7036406</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714756</v>
+        <v>113714765</v>
       </c>
       <c r="B7" t="n">
-        <v>78794</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654257</v>
+        <v>654290</v>
       </c>
       <c r="R7" t="n">
-        <v>7036088</v>
+        <v>7036546</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714755</v>
+        <v>113712559</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>90135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4745</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654248</v>
+        <v>654536</v>
       </c>
       <c r="R8" t="n">
-        <v>7036074</v>
+        <v>7036336</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714765</v>
+        <v>113714775</v>
       </c>
       <c r="B9" t="n">
-        <v>78201</v>
+        <v>90146</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654290</v>
+        <v>654383</v>
       </c>
       <c r="R9" t="n">
-        <v>7036546</v>
+        <v>7036207</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1493,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712563</v>
+        <v>113714770</v>
       </c>
       <c r="B10" t="n">
-        <v>78794</v>
+        <v>90690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2046</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654366</v>
+        <v>654461</v>
       </c>
       <c r="R10" t="n">
-        <v>7036185</v>
+        <v>7036447</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,6 +1609,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714777</v>
+        <v>113714767</v>
       </c>
       <c r="B11" t="n">
-        <v>77953</v>
+        <v>56955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654309</v>
+        <v>654323</v>
       </c>
       <c r="R11" t="n">
-        <v>7036185</v>
+        <v>7036510</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1710,6 +1720,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712560</v>
+        <v>113712548</v>
       </c>
       <c r="B12" t="n">
-        <v>78794</v>
+        <v>90522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1771,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654479</v>
+        <v>654249</v>
       </c>
       <c r="R12" t="n">
-        <v>7036198</v>
+        <v>7036581</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,7 +1856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712562</v>
+        <v>113712555</v>
       </c>
       <c r="B13" t="n">
         <v>90146</v>
@@ -1886,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654383</v>
+        <v>654469</v>
       </c>
       <c r="R13" t="n">
-        <v>7036207</v>
+        <v>7036416</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714768</v>
+        <v>113714766</v>
       </c>
       <c r="B14" t="n">
         <v>90146</v>
@@ -1992,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654442</v>
+        <v>654351</v>
       </c>
       <c r="R14" t="n">
-        <v>7036406</v>
+        <v>7036502</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2028,11 +2038,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714766</v>
+        <v>113714776</v>
       </c>
       <c r="B15" t="n">
-        <v>90146</v>
+        <v>78794</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654351</v>
+        <v>654366</v>
       </c>
       <c r="R15" t="n">
-        <v>7036502</v>
+        <v>7036185</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712556</v>
+        <v>113712541</v>
       </c>
       <c r="B16" t="n">
-        <v>90690</v>
+        <v>91032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2046</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit aspticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654461</v>
+        <v>654248</v>
       </c>
       <c r="R16" t="n">
-        <v>7036447</v>
+        <v>7036074</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,11 +2250,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712564</v>
+        <v>113714756</v>
       </c>
       <c r="B2" t="n">
-        <v>77953</v>
+        <v>78794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654309</v>
+        <v>654257</v>
       </c>
       <c r="R2" t="n">
-        <v>7036185</v>
+        <v>7036088</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712542</v>
+        <v>113712563</v>
       </c>
       <c r="B3" t="n">
         <v>78794</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654257</v>
+        <v>654366</v>
       </c>
       <c r="R3" t="n">
-        <v>7036088</v>
+        <v>7036185</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714774</v>
+        <v>113712540</v>
       </c>
       <c r="B4" t="n">
         <v>78794</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654479</v>
+        <v>654269</v>
       </c>
       <c r="R4" t="n">
-        <v>7036198</v>
+        <v>7035993</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714754</v>
+        <v>113714774</v>
       </c>
       <c r="B5" t="n">
         <v>78794</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654269</v>
+        <v>654479</v>
       </c>
       <c r="R5" t="n">
-        <v>7035993</v>
+        <v>7036198</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714768</v>
+        <v>113714775</v>
       </c>
       <c r="B6" t="n">
         <v>90146</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654442</v>
+        <v>654383</v>
       </c>
       <c r="R6" t="n">
-        <v>7036406</v>
+        <v>7036207</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714765</v>
+        <v>113712541</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654290</v>
+        <v>654248</v>
       </c>
       <c r="R7" t="n">
-        <v>7036546</v>
+        <v>7036074</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712559</v>
+        <v>113714768</v>
       </c>
       <c r="B8" t="n">
-        <v>90135</v>
+        <v>90146</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654536</v>
+        <v>654442</v>
       </c>
       <c r="R8" t="n">
-        <v>7036336</v>
+        <v>7036406</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714775</v>
+        <v>113714770</v>
       </c>
       <c r="B9" t="n">
-        <v>90146</v>
+        <v>90690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>2046</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654383</v>
+        <v>654461</v>
       </c>
       <c r="R9" t="n">
-        <v>7036207</v>
+        <v>7036447</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714770</v>
+        <v>113712548</v>
       </c>
       <c r="B10" t="n">
-        <v>90690</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1545,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2046</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vit aspticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654461</v>
+        <v>654249</v>
       </c>
       <c r="R10" t="n">
-        <v>7036447</v>
+        <v>7036581</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1609,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714767</v>
+        <v>113712553</v>
       </c>
       <c r="B11" t="n">
         <v>56955</v>
@@ -1755,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712548</v>
+        <v>113714765</v>
       </c>
       <c r="B12" t="n">
-        <v>90522</v>
+        <v>78201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,16 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654249</v>
+        <v>654290</v>
       </c>
       <c r="R12" t="n">
-        <v>7036581</v>
+        <v>7036546</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714766</v>
+        <v>113712552</v>
       </c>
       <c r="B14" t="n">
         <v>90146</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714776</v>
+        <v>113714773</v>
       </c>
       <c r="B15" t="n">
-        <v>78794</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654366</v>
+        <v>654536</v>
       </c>
       <c r="R15" t="n">
-        <v>7036185</v>
+        <v>7036336</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712541</v>
+        <v>113714777</v>
       </c>
       <c r="B16" t="n">
-        <v>91032</v>
+        <v>77953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654248</v>
+        <v>654309</v>
       </c>
       <c r="R16" t="n">
-        <v>7036074</v>
+        <v>7036185</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43604-2023 artfynd.xlsx
+++ b/artfynd/A 43604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712559</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712552</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712554</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712555</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712562</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712541</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712546</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712549</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712551</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712564</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712567</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712540</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712542</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712560</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712563</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712565</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712566</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712568</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712544</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2919,6 +3029,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712558</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3025,6 +3140,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712553</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3126,6 +3246,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712543</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,8 +3352,40 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712548</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>